--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{161925EB-BA47-4DB9-A4C1-713D9970B621}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBBB947B-D012-416F-96F8-38EFFA946E3E}"/>
   <bookViews>
-    <workbookView xWindow="29295" yWindow="2205" windowWidth="14400" windowHeight="11880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2950" yWindow="2030" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -671,7 +671,7 @@
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -712,7 +712,7 @@
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -753,7 +753,7 @@
       </c>
       <c r="M8">
         <f>SUM(J2:J302)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -976,9 +976,21 @@
       <c r="E15">
         <v>6</v>
       </c>
+      <c r="F15">
+        <v>17</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
       <c r="J15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBBB947B-D012-416F-96F8-38EFFA946E3E}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C67A374F-B1DE-46CF-A8EF-E8E9A8DE1A3E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2950" yWindow="2030" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>569</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>347</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -547,7 +547,7 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -588,7 +588,7 @@
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -630,7 +630,7 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>220</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -671,7 +671,7 @@
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -712,7 +712,7 @@
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -753,7 +753,7 @@
       </c>
       <c r="M8">
         <f>SUM(J2:J302)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -994,13 +994,37 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
       <c r="D16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.35">
